--- a/data/trans_bre/P38B-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P38B-Provincia-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 11,2</t>
+          <t>-0,24; 11,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 12,39</t>
+          <t>-3,49; 11,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 5,32</t>
+          <t>-0,66; 5,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,0; 14,01</t>
+          <t>-0,16; 13,96</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 19,11</t>
+          <t>-4,75; 17,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 5,71</t>
+          <t>-0,66; 5,8</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,74; 9,87</t>
+          <t>2,54; 10,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,9; 9,95</t>
+          <t>3,27; 10,28</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,87; 15,66</t>
+          <t>2,46; 16,1</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,04; 11,65</t>
+          <t>2,91; 12,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,25; 11,62</t>
+          <t>3,61; 12,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,59; 22,37</t>
+          <t>3,22; 23,43</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 9,57</t>
+          <t>-1,48; 9,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 7,54</t>
+          <t>-1,49; 7,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,57; 8,2</t>
+          <t>0,35; 8,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 11,78</t>
+          <t>-1,69; 11,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 8,81</t>
+          <t>-1,62; 8,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,64; 9,21</t>
+          <t>0,36; 9,27</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,0; 13,74</t>
+          <t>2,01; 14,52</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,01; 3,8</t>
+          <t>-4,13; 4,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-38,15; 7,54</t>
+          <t>-40,23; 7,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,7; 18,98</t>
+          <t>2,39; 19,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-5,44; 4,26</t>
+          <t>-4,46; 4,78</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-41,66; 8,77</t>
+          <t>-44,06; 8,67</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,84; 15,38</t>
+          <t>2,82; 15,52</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,81; 18,37</t>
+          <t>3,76; 17,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 13,86</t>
+          <t>-0,85; 13,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,31; 19,52</t>
+          <t>3,27; 19,85</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,91; 25,54</t>
+          <t>4,72; 24,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 18,24</t>
+          <t>-0,71; 18,35</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 6,42</t>
+          <t>-5,4; 5,71</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 12,53</t>
+          <t>0,17; 12,54</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,47; 5,96</t>
+          <t>-1,64; 5,12</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 7,45</t>
+          <t>-5,99; 6,62</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 16,19</t>
+          <t>0,19; 16,36</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 6,44</t>
+          <t>-1,67; 5,51</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,98; 10,1</t>
+          <t>3,0; 9,83</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,03; 12,6</t>
+          <t>2,61; 12,51</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,36; 17,74</t>
+          <t>5,99; 18,59</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,42; 12,14</t>
+          <t>3,42; 11,72</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,85; 20,27</t>
+          <t>3,93; 20,08</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,4; 22,88</t>
+          <t>7,0; 24,27</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,17; 9,45</t>
+          <t>0,88; 9,56</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,43; 7,92</t>
+          <t>2,67; 8,13</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,52; 50,88</t>
+          <t>7,57; 50,48</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,49; 13,17</t>
+          <t>1,14; 13,24</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,69; 9,1</t>
+          <t>2,91; 9,31</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,09; 249,45</t>
+          <t>12,34; 248,08</t>
         </is>
       </c>
     </row>
@@ -1274,32 +1274,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,96; 7,34</t>
+          <t>3,8; 7,3</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,81; 7,27</t>
+          <t>3,76; 7,3</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4,37; 31,2</t>
+          <t>4,51; 27,68</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,75; 9,03</t>
+          <t>4,6; 9,02</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,59; 9,01</t>
+          <t>4,55; 9,04</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,38; 54,37</t>
+          <t>5,51; 46,01</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P38B-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P38B-Provincia-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,92</t>
+          <t>1,58</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 11,22</t>
+          <t>-0,42; 11,08</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 11,61</t>
+          <t>-3,17; 11,91</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 5,34</t>
+          <t>-0,48; 4,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 13,96</t>
+          <t>-0,49; 13,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 17,98</t>
+          <t>-4,35; 18,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 5,8</t>
+          <t>-0,49; 4,34</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8,98</t>
+          <t>7,83</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>10,28%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,54; 10,14</t>
+          <t>2,79; 10,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,27; 10,28</t>
+          <t>3,33; 10,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,46; 16,1</t>
+          <t>1,63; 14,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,91; 12,14</t>
+          <t>3,12; 12,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,61; 12,04</t>
+          <t>3,66; 12,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,22; 23,43</t>
+          <t>2,0; 19,76</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,84</t>
+          <t>3,53</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 9,02</t>
+          <t>-1,16; 9,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 7,5</t>
+          <t>-1,56; 7,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,35; 8,28</t>
+          <t>0,08; 7,69</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 11,1</t>
+          <t>-1,29; 11,73</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 8,65</t>
+          <t>-1,7; 8,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 9,27</t>
+          <t>0,08; 8,6</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-8,51</t>
+          <t>6,5</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-9,63%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,01; 14,52</t>
+          <t>1,71; 13,23</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 4,29</t>
+          <t>-3,96; 4,14</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-40,23; 7,51</t>
+          <t>0,43; 14,07</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,39; 19,98</t>
+          <t>2,12; 17,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-4,46; 4,78</t>
+          <t>-4,29; 4,65</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-44,06; 8,67</t>
+          <t>0,48; 17,68</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6,28</t>
+          <t>8,2</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>10,46%</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,82; 15,52</t>
+          <t>2,08; 14,54</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>3,76; 17,55</t>
+          <t>4,29; 17,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 13,68</t>
+          <t>1,1; 15,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,27; 19,85</t>
+          <t>2,42; 18,41</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,72; 24,0</t>
+          <t>5,43; 24,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,71; 18,35</t>
+          <t>1,55; 21,0</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1,46</t>
+          <t>3,23</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 5,71</t>
+          <t>-4,9; 6,47</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,17; 12,54</t>
+          <t>-0,21; 12,06</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 5,12</t>
+          <t>-0,58; 7,03</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 6,62</t>
+          <t>-5,49; 7,75</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,19; 16,36</t>
+          <t>-0,23; 15,93</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 5,51</t>
+          <t>-0,58; 7,76</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>10,92</t>
+          <t>7,65</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>9,16%</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,0; 9,83</t>
+          <t>3,14; 9,92</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,61; 12,51</t>
+          <t>1,87; 12,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5,99; 18,59</t>
+          <t>3,83; 12,06</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,42; 11,72</t>
+          <t>3,54; 11,86</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,93; 20,08</t>
+          <t>2,69; 19,2</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,0; 24,27</t>
+          <t>4,44; 15,08</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>25,16</t>
+          <t>9,26</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>15,48%</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,88; 9,56</t>
+          <t>1,07; 9,9</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,67; 8,13</t>
+          <t>2,56; 7,92</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,57; 50,48</t>
+          <t>4,46; 14,11</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,14; 13,24</t>
+          <t>1,4; 13,8</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>2,91; 9,31</t>
+          <t>2,78; 9,0</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,34; 248,08</t>
+          <t>7,19; 24,98</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11,37</t>
+          <t>6,75</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>8,44%</t>
         </is>
       </c>
     </row>
@@ -1274,32 +1274,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>3,8; 7,3</t>
+          <t>3,96; 7,41</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3,76; 7,3</t>
+          <t>3,63; 7,33</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4,51; 27,68</t>
+          <t>4,71; 8,67</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>4,6; 9,02</t>
+          <t>4,79; 9,2</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,55; 9,04</t>
+          <t>4,4; 9,03</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,51; 46,01</t>
+          <t>5,77; 11,06</t>
         </is>
       </c>
     </row>
